--- a/experiments/results/standard_bound/cplex-cp-standard-bound.xlsx
+++ b/experiments/results/standard_bound/cplex-cp-standard-bound.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,25 +446,35 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Lower bound</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Upper bound</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -498,25 +508,35 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>7.6</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>0.27</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -550,25 +570,35 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>0.06</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -602,25 +632,35 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>0.06</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -654,25 +694,35 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>9.4</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>0.31</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -706,25 +756,35 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>7.4</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>0.06</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -758,25 +818,35 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>9.1</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>0.17</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -810,25 +880,35 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>9.7</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>0.22</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -862,25 +942,35 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>18.6</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>30.27</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -914,25 +1004,35 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>270.8</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>1800.00</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -962,25 +1062,35 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>180.1</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>1800.02</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1010,25 +1120,35 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>16.2</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1062,25 +1182,35 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>13.8</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>0.18</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1114,25 +1244,35 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>191</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>167.5</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>1800.09</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1162,25 +1302,35 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>191</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>168.4</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>1800.00</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1210,25 +1360,35 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>182</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>200.5</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>1800.08</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1258,25 +1418,35 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>161.0</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>1800.04</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1306,25 +1476,35 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>227</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>113.5</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>21.63</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1358,25 +1538,35 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>218</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>210.2</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>1800.06</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1406,25 +1596,35 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>260</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>260</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>168.7</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>374.99</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1458,25 +1658,35 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>245.3</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>1800.08</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1506,25 +1716,35 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>331</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>331</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>183.0</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>48.94</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1558,25 +1778,35 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>328</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>264.3</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>1800.13</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1606,25 +1836,35 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>341</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>275.8</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>1800.04</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1654,25 +1894,35 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>306</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>333.0</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>1800.06</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1685,7 +1935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1716,25 +1966,35 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Lower bound</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Upper bound</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -1768,25 +2028,35 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>8.6</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>2.37</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1820,25 +2090,35 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>6.7</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>0.07</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1872,25 +2152,35 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>0.11</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1924,25 +2214,35 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>1.79</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1976,25 +2276,35 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>7.8</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>0.11</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2028,25 +2338,35 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>9.7</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>0.36</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2080,25 +2400,35 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>0.82</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2132,25 +2462,35 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>45.5</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>147.24</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2184,25 +2524,35 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>180.7</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>1800.00</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2232,25 +2582,35 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>147.0</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>1800.01</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2280,25 +2640,35 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>18.5</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>5.53</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2332,25 +2702,35 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>15.8</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>0.43</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2384,25 +2764,35 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>304</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>182.5</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>1800.04</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2432,25 +2822,35 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>304</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>184.0</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>1800.07</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2480,25 +2880,35 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>194</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>284</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>207.7</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>1800.08</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2528,25 +2938,35 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>313</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>184.8</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>1800.07</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2576,25 +2996,35 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>341</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>204.0</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>1202.52</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2628,25 +3058,35 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>346</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>259.5</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>1800.00</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2676,25 +3116,35 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>390</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>391</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>208.0</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>1800.04</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2724,25 +3174,35 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>403</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>279.4</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>1800.04</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2772,25 +3232,35 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>496</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>496</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>166.7</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>44.04</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2824,25 +3294,35 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>492</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>502</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>274.8</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>1800.12</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2872,25 +3352,35 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>308.4</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>1800.04</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2920,25 +3410,35 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>466</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>347.4</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>1800.02</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2951,7 +3451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2982,25 +3482,35 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Lower bound</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Upper bound</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -3034,25 +3544,35 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>569.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>1800.00</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3082,25 +3602,35 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>29.7</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>74.43</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3134,25 +3664,35 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>637.2</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>1800.00</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3182,25 +3722,35 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>412.7</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>1800.00</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3230,25 +3780,35 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>476.1</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>1800.00</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3278,25 +3838,35 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>12.2</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>8.43</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3330,25 +3900,35 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>409.0</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>1800.02</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3378,25 +3958,35 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>405.0</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>1800.00</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3426,25 +4016,35 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>546.7</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>1800.00</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3474,25 +4074,35 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>281.7</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>1800.00</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3522,25 +4132,35 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>117</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>180.4</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>1800.01</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3570,25 +4190,35 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>14.6</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>0.36</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3622,25 +4252,35 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>240.1</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>1800.02</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3670,25 +4310,35 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>239.6</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>1800.02</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3718,25 +4368,35 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>655.4</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>1800.03</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3766,25 +4426,35 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>445</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>330.0</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>1800.02</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3814,25 +4484,35 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>319.7</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>1800.01</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3862,25 +4542,35 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>302.8</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>1800.02</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3910,25 +4600,35 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>263</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>279.3</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>1800.02</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3958,25 +4658,35 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>402.4</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>1800.04</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4006,25 +4716,35 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>662</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>662</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>193.1</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>70.13</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -4058,25 +4778,35 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>331</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>385.0</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>1800.03</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4106,25 +4836,35 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>685</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>454.6</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>1800.03</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4154,25 +4894,35 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>715</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>476.3</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>1800.04</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
